--- a/data/WorkTypes.xlsx
+++ b/data/WorkTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\forlogssystems\work_utilization_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B9E62-34D6-4426-A264-21449C6F968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAC6465-CFCE-4898-B412-6F1E2CBD121A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -453,7 +453,9 @@
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>2140</v>
+      </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
